--- a/КПП/Том СКС КПП/Реестр документов о качестве СКС КПП.xlsx
+++ b/КПП/Том СКС КПП/Реестр документов о качестве СКС КПП.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="110">
   <si>
     <t xml:space="preserve">Объект капитального строительства: «Центр временного содержания иностранных граждан», Калужская область, м. р-н Боровский, д. Старомихайловское, ул. 1-я Индустриальная, вл. 2, земельный участок с кадастровым номером 40:03:068314:1874</t>
   </si>
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Лицо, выполнившее работы: ООО «АльтЭн», ОГРН 1024000944098, ИНН 4025062969</t>
   </si>
   <si>
-    <t xml:space="preserve">Здание: КПП. Том ИД: СКС — структурированная кабельная система (СКС). Рабочая документация 16/1/26-СКС-Р. Исполнительная документация 16/1/26-ИД-КПП, лист 4; кабельный журнал 16/1/26-ИД-КПП.КЖ (раздел СКС)</t>
+    <t xml:space="preserve">Здание: КПП. Том ИД: СКС — структурированная кабельная система (СКС). Рабочая документация 16/1/26-СКС-Р. Исполнительная документация 16/1/26-СКС-ИД-КПП, лист 2; кабельный журнал 16/1/26-СКС-ИД-КПП.КЖ; спецификация 16/1/26-СКС-ИД-КПП.СО</t>
   </si>
   <si>
     <t xml:space="preserve">РЕЕСТР</t>
@@ -163,40 +163,136 @@
     <t xml:space="preserve">Кабель-канал 110×50 IN-Liner FRONT</t>
   </si>
   <si>
-    <t xml:space="preserve">DKC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Предоставить</t>
+    <t xml:space="preserve">АО «ДКС» (DKC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ИНФОРМАЦИОННОЕ ПИСЬМО изготовителя (пожарная безопасность, ГОСТ Р 53313-2009)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">исх. № 284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.08.2012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ЗАО «ДКС»</t>
   </si>
   <si>
     <t xml:space="preserve">2-СКС-КПП</t>
   </si>
   <si>
+    <t xml:space="preserve">ЭКСПЕРТНОЕ ЗАКЛЮЧЕНИЕ по результатам санитарно-эпидемиологической экспертизы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">№ 170г/2017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.02.2017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Орган инспекции ФГБУЗ ГЦГиЭ ФМБА России (RA.RU.710138)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Угол внутренний изменяемый 110×50 IN-Liner FRONT</t>
   </si>
   <si>
     <t xml:space="preserve">шт.</t>
   </si>
   <si>
+    <t xml:space="preserve">РЕШЕНИЕ органа по сертификации об отказе в обязательной сертификации (ст. 145 ч. 4 123-ФЗ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">№ 524/15-РЗ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.12.2015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ОС «ТПБ СЕРТ» ООО «Технологии пожарной безопасности» (ТРПБ.RU.ПБ25)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Угол плоский Г-образный 110×50 IN-Liner FRONT</t>
   </si>
   <si>
     <t xml:space="preserve">АОСР № 3-СКС-КПП — прокладка кабельных линий</t>
   </si>
   <si>
-    <t xml:space="preserve">Кабель витая пара F/UTP Cat 6 4×2×23AWG solid LSZH нг</t>
+    <t xml:space="preserve">Кабель витая пара F/UTP Cat 6 4×2×23AWG solid LSZH нг(А)-HF, Cabeus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ООО «АнЛан»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">СЕРТИФИКАТ СООТВЕТСТВИЯ (ТР ТС 004/2011) с приложением</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ЕАЭС RU C-RU.АЖ38.В.00445/22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.03.2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">по 20.03.2027 включительно</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ОС ООО МЦИС «ЕвроСерт» (RA.RU.11АЖ38)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-СКС-КПП</t>
+  </si>
+  <si>
+    <t xml:space="preserve">СЕРТИФИКАТ СООТВЕТСТВИЯ (добровольная сертификация, система «Прибор-Эксперт», ГОСТ Р 54429-2009)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">РОСС CN.НВ61.Н29435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.10.2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">по 13.10.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ОС ООО «ЦЕТРИМ» (RA.RU.11НВ61)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПАСПОРТ изготовителя (кабель «витая пара» кат. 6, внутренней прокладки)</t>
   </si>
   <si>
     <t xml:space="preserve">Cabeus</t>
   </si>
   <si>
-    <t xml:space="preserve">3-СКС-КПП</t>
-  </si>
-  <si>
     <t xml:space="preserve">Кабель витая пара ParLan U/UTP Cat 5e 4×2×0,52 PVC</t>
   </si>
   <si>
-    <t xml:space="preserve">«Паритет»</t>
+    <t xml:space="preserve">ООО «ТПД Паритет»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ЕАЭС RU C-RU.АЮ64.В.00680/25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.01.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">по 16.01.2030 включительно</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ОС «ПОЛИСЕРТ» АНО «Электросерт» (RA.RU.10АЮ64)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">СЕРТИФИКАТ СООТВЕТСТВИЯ (обязательная сертификация, 123-ФЗ) с приложением № 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RU C-RU.АЮ64.В.00546/24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.12.2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">по 16.12.2029</t>
   </si>
   <si>
     <t xml:space="preserve">Труба гофрированная ПВХ серая с/з d20 мм «Строитель», арт. PR.032000</t>
@@ -220,6 +316,9 @@
     <t xml:space="preserve">ОС «СЗРЦ СЕРТ»</t>
   </si>
   <si>
+    <t xml:space="preserve">ПАСПОРТ изготовителя (труба гофрированная ПВХ серая)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Скоба металлическая однолапковая СМО 19-20, арт. PR08.2534</t>
   </si>
   <si>
@@ -227,9 +326,6 @@
   </si>
   <si>
     <t xml:space="preserve">ПАСПОРТ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">—</t>
   </si>
   <si>
     <t xml:space="preserve">Изготовитель «Промрукав»</t>
@@ -324,13 +420,6 @@
     </font>
     <font>
       <i val="true"/>
-      <sz val="9"/>
-      <name val="Times New Roman"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <i val="true"/>
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="0"/>
@@ -343,19 +432,20 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <i val="true"/>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -399,7 +489,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -436,23 +526,11 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -460,11 +538,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -477,66 +555,6 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFF2CC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -720,7 +738,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -1070,7 +1088,7 @@
       <c r="K16" s="6"/>
       <c r="L16" s="6"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="n">
         <v>4</v>
       </c>
@@ -1086,185 +1104,235 @@
       <c r="E17" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="F17" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="G17" s="10"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="11"/>
+      <c r="G17" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="K17" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="L17" s="7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="n">
         <v>5</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C18" s="8" t="s">
         <v>46</v>
       </c>
       <c r="D18" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="I18" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="E18" s="7" t="n">
+      <c r="J18" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="K18" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F18" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="G18" s="10"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="11"/>
       <c r="L18" s="7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="n">
         <v>6</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>46</v>
       </c>
       <c r="D19" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="I19" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="E19" s="7" t="n">
+      <c r="J19" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="K19" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E20" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F19" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="G19" s="10"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="11"/>
-      <c r="L19" s="7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
+      <c r="F20" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="K20" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="6"/>
-    </row>
-    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E21" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="G21" s="10"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="11"/>
-      <c r="L21" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="6"/>
+    </row>
+    <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="n">
         <v>8</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>22</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="G22" s="10"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="10"/>
-      <c r="K22" s="11"/>
+        <v>45</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="K22" s="7" t="n">
+        <v>3</v>
+      </c>
       <c r="L22" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="n">
         <v>9</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="D23" s="7" t="s">
         <v>22</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="n">
         <v>10</v>
       </c>
@@ -1275,145 +1343,335 @@
         <v>66</v>
       </c>
       <c r="D24" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="G24" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="E24" s="7" t="n">
+      <c r="H24" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K24" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E25" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="K25" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L25" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="K26" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L26" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E27" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="F24" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="G24" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="I24" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="J24" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="K24" s="7" t="n">
+      <c r="F27" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="K27" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L27" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I28" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="J28" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K28" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="L24" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="12" t="str">
-        <f aca="false">CONCATENATE("Всего позиций: ",COUNTA(B12:B24),"; листов копий: ",SUM(K12:K24))</f>
-        <v>Всего позиций: 10; листов копий: 12</v>
-      </c>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="12"/>
-      <c r="J28" s="12"/>
-      <c r="K28" s="12"/>
-      <c r="L28" s="12"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="14" t="s">
+      <c r="L28" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="H29" s="14"/>
-      <c r="I29" s="14"/>
-      <c r="J29" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="K29" s="14"/>
-      <c r="L29" s="14"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G30" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="H30" s="15"/>
-      <c r="I30" s="15"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="B32" s="12"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="12"/>
-      <c r="H32" s="12"/>
-      <c r="I32" s="12"/>
-      <c r="J32" s="12"/>
-      <c r="K32" s="12"/>
-      <c r="L32" s="12"/>
+    </row>
+    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E29" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I29" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="J29" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="K29" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L29" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="9" t="str">
+        <f aca="false">CONCATENATE("Всего позиций: ",COUNTA(B12:B29),"; листов копий: ",SUM(K12:K29))</f>
+        <v>Всего позиций: 15; листов копий: 32</v>
+      </c>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="B33" s="13"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="H33" s="14"/>
-      <c r="I33" s="14"/>
-      <c r="J33" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="K33" s="14"/>
-      <c r="L33" s="14"/>
+      <c r="A33" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="9"/>
+      <c r="K33" s="9"/>
+      <c r="L33" s="9"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G34" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="H34" s="15"/>
-      <c r="I34" s="15"/>
-    </row>
-    <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="B36" s="16"/>
-      <c r="C36" s="16"/>
-      <c r="D36" s="16"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="16"/>
-      <c r="G36" s="16"/>
-      <c r="H36" s="16"/>
-      <c r="I36" s="16"/>
-      <c r="J36" s="16"/>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
+      <c r="A34" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="B34" s="10"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="10"/>
+      <c r="G34" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
+      <c r="J34" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G35" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="H35" s="12"/>
+      <c r="I35" s="12"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="9"/>
+      <c r="I37" s="9"/>
+      <c r="J37" s="9"/>
+      <c r="K37" s="9"/>
+      <c r="L37" s="9"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="B38" s="10"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="10"/>
+      <c r="G38" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="H38" s="11"/>
+      <c r="I38" s="11"/>
+      <c r="J38" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="K38" s="11"/>
+      <c r="L38" s="11"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G39" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="H39" s="12"/>
+      <c r="I39" s="12"/>
+    </row>
+    <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="B41" s="13"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="13"/>
+      <c r="H41" s="13"/>
+      <c r="I41" s="13"/>
+      <c r="J41" s="13"/>
+      <c r="K41" s="13"/>
+      <c r="L41" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="22">
@@ -1426,19 +1684,19 @@
     <mergeCell ref="A8:L8"/>
     <mergeCell ref="A12:L12"/>
     <mergeCell ref="A16:L16"/>
-    <mergeCell ref="A20:L20"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A28:L28"/>
-    <mergeCell ref="A29:F29"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:L29"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="A32:L32"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="J33:L33"/>
+    <mergeCell ref="A21:L21"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A33:L33"/>
+    <mergeCell ref="A34:F34"/>
     <mergeCell ref="G34:I34"/>
-    <mergeCell ref="A36:L36"/>
+    <mergeCell ref="J34:L34"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="A37:L37"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="G38:I38"/>
+    <mergeCell ref="J38:L38"/>
+    <mergeCell ref="G39:I39"/>
+    <mergeCell ref="A41:L41"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
